--- a/eval_cases/多轮意图测试用例副本_测试结果.xlsx
+++ b/eval_cases/多轮意图测试用例副本_测试结果.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5201.183</v>
+        <v>6160.109</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -592,7 +592,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下刘德华的歌曲”属于获取推荐建议/信息服务，目标是获得歌曲清单或建议，而非查找云盘中已存储的具体音频文件载体。根据规则2和5，此类推荐类诉求应输出no_match。</t>
+          <t>用户请求“推荐一下刘德华的歌曲”属于音乐推荐/资讯建议类需求，目标是获取语言答案或推荐列表，而非查找、定位或获取云盘内已有的具体资源载体（如文件、音频文件本身）。根据规则2，若主目标是语言答案或信息服务（包括推荐建议），且没有可执行业务 skill，应输出 no_match。available_skills 中 mcloud_search_skill 明确说明“若用户关注的是...推荐建议...而不是获取资源载体本身，则不属于云盘搜索”，其他 skill 也不支持音乐推荐功能。</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>28045.407</v>
+        <v>82472.057</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2954.561</v>
+        <v>3569.277</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -746,7 +746,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下刘德华的歌”属于获取推荐建议/信息服务，目标是获得歌曲清单或建议，而非在云盘中查找、定位或获取具体的音频资源载体本身。根据规则5，此类推荐类诉求应输出 no_match。</t>
+          <t>用户请求“推荐一下刘德华的歌”属于音乐推荐/信息服务，目标是获取建议或列表，而非查找、定位或获取云盘中已有的具体资源载体（如文件、音频）。根据规则2，若主目标是语言答案或信息服务（包括推荐建议），且没有可执行业务 skill，应输出 no_match。available_skills 中 mcloud_search_skill 明确要求“若用户关注的是...推荐建议...而不是获取资源载体本身，则不属于云盘搜索”，其他技能也不支持音乐推荐功能。</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7973.442</v>
+        <v>6964.619</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下周杰伦的歌”属于获取推荐建议/信息服务，目标是获得一份歌曲清单或建议，而非查找、定位或获取云盘中已存储的具体资源载体（如具体的音频文件）。根据规则2和规则5，普通寒暄、开放问答、推荐建议等答案目标属于普通对话，应输出 no_match。</t>
+          <t>用户请求“推荐一下周杰伦的歌”属于音乐内容推荐建议，目标是获取语言答案或信息服务，而非查找、定位或获取云盘内已有的具体资源载体（如文件、音频文件等）。根据规则2，若主目标是语言答案或信息服务，包括推荐建议，且没有可执行业务 skill，应输出 no_match。available_skills 中没有专门用于音乐推荐的技能，mcloud_search_skill 针对的是资源载体的检索而非内容推荐。</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3046.791</v>
+        <v>4063.619</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下刘德华的电影和歌曲”属于获取推荐清单和内容建议，目标是获得信息服务而非查找云盘中已存储的具体资源载体（如特定文件）。根据规则5，推荐类诉求应输出 no_match。</t>
+          <t>用户请求是“推荐一下刘德华的电影和歌曲”，主动作是“推荐”，期望结果是关于刘德华作品的列表或建议（语言答案/信息服务）。根据规则2，若主目标是语言答案或信息服务，包括推荐建议，且没有可执行业务 skill，应输出 no_match。虽然存在 mcloud_search_skill，但其定义明确指出“若用户关注的是语言答案、推荐建议...而不是获取资源载体本身，则不属于云盘搜索”。当前没有专门用于娱乐内容推荐的 skill，因此匹配 no_match。</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7219.755</v>
+        <v>7884.019</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下刘德华的电影”属于获取推荐清单/建议，目标是获得信息服务而非查找云盘中已存储的具体资源载体（如特定的电影文件）。根据规则5，推荐类诉求应输出no_match。</t>
+          <t>用户请求“推荐一下刘德华的电影”属于内容推荐和信息服务，期望得到的是电影名称列表或建议，而非在云盘中查找具体的视频文件载体。根据规则2，若主目标是语言答案或信息服务（包括推荐建议），且没有可执行业务 skill，应输出 no_match。虽然 mcloud_search_skill 支持搜影视，但其定义明确指出“若用户关注的是...推荐建议...而不是获取资源载体本身，则不属于云盘搜索”。available_skills 中没有专门的内容推荐或百科问答 skill，因此无法匹配。</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10745.869</v>
+        <v>7465.129</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>new_request</t>
+          <t>continuation</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>用户意图是“推荐一下周星驰的电影”，属于获取推荐清单和内容建议，目标是语言答案/信息服务，而非查找或获取云盘中已存储的具体资源载体文件。根据规则5，推荐建议应输出 no_match。</t>
+          <t>用户请求“推荐一下周星驰的电影”属于影视内容推荐/资讯问答，期望结果是语言形式的建议列表，而非从云盘中查找并获取具体的电影文件载体。根据规则2，若主目标是语言答案或信息服务（包括推荐建议），且没有可执行业务 skill，应输出 no_match。虽然存在 mcloud_search_skill，但其定义为“查找、定位、获取资源载体本身”，不适用于开放式的内容推荐场景。</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2949.857</v>
+        <v>4367.633</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下沈腾的电影”属于获取推荐建议和影视资讯，目标是语言答案而非查找云盘中已存在的特定资源载体。根据规则5，此类推荐类诉求不属于云盘搜索或文件管理范畴，应输出no_match。</t>
+          <t>用户请求“推荐一下沈腾的电影”属于获取推荐建议/信息服务，目标是语言答案而非具体的云盘资源载体（如查找某部特定电影文件）。根据规则2，若主目标是语言答案或信息服务（包括推荐建议），且没有可执行业务 skill 直接提供该服务，应输出 no_match。虽然 mcloud_search_skill 支持搜影视，但其定义明确指出“若用户关注的是语言答案、推荐建议...而不是获取资源载体本身，则不属于云盘搜索”。因此，此请求不符合搜索类 skill 的定义，也不符合其他处理类或管理类 skill 的定义。</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6804.255</v>
+        <v>7338.477</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下沈腾2023年上映的电影”属于获取影视资讯和推荐建议，目标是获得语言答案而非查找云盘内的具体资源载体（如已保存的电影文件）。根据规则5，推荐清单、事实答案等不属于资源载体检索，应输出no_match。</t>
+          <t>用户请求“推荐一下沈腾2023年上映的电影”属于影视资讯推荐和百科问答类需求，目标是获取语言形式的建议或信息，而非查找、定位或获取云盘内已有的具体资源载体（如文件、视频文件等）。根据规则2，若主目标是语言答案或信息服务（包括推荐建议、资讯问答），且没有可执行业务 skill，应输出 no_match。available_skills 中的 mcloud_search_skill 明确排除了推荐建议和联网问答场景，其他 skill 均不匹配此意图。</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1263,14 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>12280.364</v>
+        <v>18459.746</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["param_mismatch"]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>18351.579</v>
+        <v>14310.178</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>continuation</t>
+          <t>revision</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1417,14 +1417,14 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>64116.961</v>
+        <v>12507.983</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>["param_mismatch"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6211.039</v>
+        <v>7424.69</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>推荐一下刘德华主演的最值得看的一部电影</t>
+          <t>推荐一部刘德华主演的最值得看的电影</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>用户请求是“推荐一下刘德华主演的最值得看的一部电影”，目标是获取基于评价或口碑的推荐建议（语言答案/信息服务），而非在云盘中查找或定位具体的电影资源文件。根据规则2和规则5，推荐清单、事实答案、解释说明等属于普通对话，应输出 no_match。</t>
+          <t>用户意图是“推荐一部刘德华主演的最值得看的电影”，这是一个关于电影内容的咨询和推荐请求，期望得到的是语言答案或建议，而非在云盘中查找、定位或获取具体的电影文件资源载体。根据规则2，若主目标是语言答案或信息服务（包括推荐建议），且没有可执行业务 skill，应输出 no_match。available_skills 中没有专门处理通用影视内容推荐的技能，mcloud_search_skill 仅用于检索资源载体，不符合此处的推荐意图。</t>
         </is>
       </c>
     </row>
@@ -1571,14 +1571,14 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>11707.6</v>
+        <v>24910.419</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["param_mismatch"]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6501.102</v>
+        <v>8118.538</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>推荐一下刘德华的电影</t>
+          <t>推荐刘德华的电影</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>revision</t>
+          <t>new_request</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>用户请求“推荐一下刘德华的电影”属于获取推荐建议/信息服务，目标是获得一份电影清单或推荐结果，而非在云盘中查找、定位或获取具体的电影资源文件载体。根据规则2和规则5，普通寒暄、开放问答、推荐建议等答案目标属于普通对话，应输出no_match。</t>
+          <t>用户意图为“推荐刘德华的电影”，属于获取推荐建议或信息服务，目标是语言答案而非获取具体的资源载体（如云盘内的电影文件）。根据规则2，若主目标是语言答案或信息服务（包括推荐建议），且没有可执行业务 skill，应输出 no_match。available_skills 中虽然有 mcloud_search_skill（云盘搜索），但其描述明确指出“若用户关注的是语言答案、推荐建议...而不是获取资源载体本身，则不属于云盘搜索”。其他技能如 work_skill、image_skill 等均不匹配推荐电影的意图。因此，该请求应由系统映射为普通对话。</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3168.281</v>
+        <v>3138.572</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>用户询问“新金手指是谁导演的，什么时候播出”，属于影视作品的百科信息查询（事实答案/信息服务），目标是获得语言答案而非查找云盘内的资源载体文件。根据规则2和规则5，此类开放问答、百科解释应输出no_match。</t>
+          <t>用户询问“新金手指是谁导演的，什么时候播出”，属于影视资讯类的百科问答（获取语言答案），而非查找云盘内的资源载体。available_skills 中没有支持通用百科问答或联网搜索影视信息的技能，因此输出 no_match。</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>11064.746</v>
+        <v>12231.776</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
@@ -1857,29 +1857,29 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>mcloud_search_skill</t>
+          <t>image_skill</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>搜图片</t>
+          <t>文生图</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>002</t>
         </is>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>code_mismatch</t>
+          <t>exact_code</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>15556.499</v>
+        <v>17269.6</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>搜索谢娜近期的图片</t>
+          <t>生成一些谢娜的近期图片</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>15943.103</v>
+        <v>16113.417</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>continuation</t>
+          <t>revision</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>14505.677</v>
+        <v>15119.243</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12717.4035197002</v>
+        <v>13994.45506509946</v>
       </c>
     </row>
     <row r="7">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="8">
